--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:57:11+00:00</t>
+    <t>2026-09-14T07:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:03:29+00:00</t>
+    <t>2026-09-14T07:11:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:11:51+00:00</t>
+    <t>2026-09-14T07:28:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:28:02+00:00</t>
+    <t>2026-09-14T08:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:01:31+00:00</t>
+    <t>2026-09-14T08:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18106" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18303" uniqueCount="1449">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:17:06+00:00</t>
+    <t>2026-10-09T09:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3758,13 +3758,31 @@
 </t>
   </si>
   <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>Durchführendes Labor</t>
+  </si>
+  <si>
+    <t>Organisation (Labor), die die Laboruntersuchung durchgeführt hat.</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -5671,7 +5689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK541"/>
+  <dimension ref="A1:AK547"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.24609375" customWidth="true" bestFit="true"/>
@@ -41629,7 +41647,7 @@
         <v>78</v>
       </c>
       <c r="H344" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I344" t="s" s="2">
         <v>77</v>
@@ -54038,7 +54056,7 @@
         <v>79</v>
       </c>
       <c r="I462" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J462" t="s" s="2">
         <v>77</v>
@@ -54143,29 +54161,25 @@
         <v>86</v>
       </c>
       <c r="I463" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J463" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K463" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L463" t="s" s="2">
-        <v>1203</v>
+        <v>87</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1204</v>
+        <v>88</v>
       </c>
       <c r="N463" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O463" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="P463" t="s" s="2">
-        <v>1206</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O463" s="2"/>
+      <c r="P463" s="2"/>
       <c r="Q463" t="s" s="2">
         <v>77</v>
       </c>
@@ -54201,17 +54215,19 @@
         <v>77</v>
       </c>
       <c r="AC463" t="s" s="2">
-        <v>1207</v>
-      </c>
-      <c r="AD463" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD463" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE463" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF463" t="s" s="2">
-        <v>1208</v>
+        <v>77</v>
       </c>
       <c r="AG463" t="s" s="2">
-        <v>1202</v>
+        <v>90</v>
       </c>
       <c r="AH463" t="s" s="2">
         <v>78</v>
@@ -54220,10 +54236,10 @@
         <v>86</v>
       </c>
       <c r="AJ463" t="s" s="2">
-        <v>1209</v>
+        <v>77</v>
       </c>
       <c r="AK463" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="464">
@@ -54231,48 +54247,44 @@
         <v>995</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1202</v>
-      </c>
-      <c r="D464" t="s" s="2">
-        <v>1211</v>
-      </c>
+        <v>1203</v>
+      </c>
+      <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F464" s="2"/>
       <c r="G464" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H464" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I464" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J464" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K464" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L464" t="s" s="2">
-        <v>243</v>
+        <v>92</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1212</v>
+        <v>112</v>
       </c>
       <c r="N464" t="s" s="2">
-        <v>1213</v>
+        <v>113</v>
       </c>
       <c r="O464" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="P464" t="s" s="2">
-        <v>1206</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="P464" s="2"/>
       <c r="Q464" t="s" s="2">
         <v>77</v>
       </c>
@@ -54308,31 +54320,31 @@
         <v>77</v>
       </c>
       <c r="AC464" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD464" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE464" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF464" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG464" t="s" s="2">
-        <v>1202</v>
+        <v>96</v>
       </c>
       <c r="AH464" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI464" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ464" t="s" s="2">
-        <v>1209</v>
+        <v>77</v>
       </c>
       <c r="AK464" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="465">
@@ -54340,10 +54352,10 @@
         <v>995</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1214</v>
+        <v>1204</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -54357,24 +54369,26 @@
         <v>86</v>
       </c>
       <c r="I465" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J465" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K465" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L465" t="s" s="2">
         <v>87</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>88</v>
+        <v>611</v>
       </c>
       <c r="N465" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O465" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="O465" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P465" s="2"/>
       <c r="Q465" t="s" s="2">
         <v>77</v>
@@ -54423,7 +54437,7 @@
         <v>77</v>
       </c>
       <c r="AG465" t="s" s="2">
-        <v>90</v>
+        <v>614</v>
       </c>
       <c r="AH465" t="s" s="2">
         <v>78</v>
@@ -54432,10 +54446,10 @@
         <v>86</v>
       </c>
       <c r="AJ465" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK465" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="466">
@@ -54443,21 +54457,21 @@
         <v>995</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F466" s="2"/>
       <c r="G466" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H466" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I466" t="s" s="2">
         <v>77</v>
@@ -54466,19 +54480,19 @@
         <v>77</v>
       </c>
       <c r="K466" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L466" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>112</v>
+        <v>617</v>
       </c>
       <c r="N466" t="s" s="2">
-        <v>113</v>
+        <v>618</v>
       </c>
       <c r="O466" t="s" s="2">
-        <v>114</v>
+        <v>619</v>
       </c>
       <c r="P466" s="2"/>
       <c r="Q466" t="s" s="2">
@@ -54504,43 +54518,43 @@
         <v>77</v>
       </c>
       <c r="Y466" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z466" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA466" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB466" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AC466" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD466" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE466" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF466" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG466" t="s" s="2">
-        <v>96</v>
+        <v>622</v>
       </c>
       <c r="AH466" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI466" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ466" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK466" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="467">
@@ -54548,14 +54562,12 @@
         <v>995</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1217</v>
-      </c>
-      <c r="D467" t="s" s="2">
-        <v>1219</v>
-      </c>
+        <v>1206</v>
+      </c>
+      <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
         <v>77</v>
       </c>
@@ -54564,28 +54576,28 @@
         <v>78</v>
       </c>
       <c r="H467" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I467" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J467" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K467" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L467" t="s" s="2">
-        <v>1220</v>
+        <v>167</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1221</v>
+        <v>624</v>
       </c>
       <c r="N467" t="s" s="2">
-        <v>1222</v>
+        <v>625</v>
       </c>
       <c r="O467" t="s" s="2">
-        <v>1223</v>
+        <v>626</v>
       </c>
       <c r="P467" s="2"/>
       <c r="Q467" t="s" s="2">
@@ -54635,19 +54647,19 @@
         <v>77</v>
       </c>
       <c r="AG467" t="s" s="2">
-        <v>96</v>
+        <v>627</v>
       </c>
       <c r="AH467" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI467" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ467" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK467" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="468">
@@ -54655,10 +54667,10 @@
         <v>995</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1224</v>
+        <v>1207</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1225</v>
+        <v>1207</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -54666,13 +54678,13 @@
       </c>
       <c r="F468" s="2"/>
       <c r="G468" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H468" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I468" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J468" t="s" s="2">
         <v>77</v>
@@ -54681,20 +54693,18 @@
         <v>80</v>
       </c>
       <c r="L468" t="s" s="2">
-        <v>1226</v>
+        <v>87</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1227</v>
+        <v>629</v>
       </c>
       <c r="N468" t="s" s="2">
-        <v>1228</v>
+        <v>630</v>
       </c>
       <c r="O468" t="s" s="2">
-        <v>1229</v>
-      </c>
-      <c r="P468" t="s" s="2">
-        <v>1230</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="P468" s="2"/>
       <c r="Q468" t="s" s="2">
         <v>77</v>
       </c>
@@ -54742,7 +54752,7 @@
         <v>77</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>1231</v>
+        <v>632</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>78</v>
@@ -54762,10 +54772,10 @@
         <v>995</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1233</v>
+        <v>1208</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -54779,25 +54789,29 @@
         <v>86</v>
       </c>
       <c r="I469" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J469" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K469" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L469" t="s" s="2">
-        <v>87</v>
+        <v>1209</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>900</v>
+        <v>1210</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="O469" s="2"/>
-      <c r="P469" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O469" t="s" s="2">
+        <v>1211</v>
+      </c>
+      <c r="P469" t="s" s="2">
+        <v>1212</v>
+      </c>
       <c r="Q469" t="s" s="2">
         <v>77</v>
       </c>
@@ -54833,19 +54847,17 @@
         <v>77</v>
       </c>
       <c r="AC469" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD469" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>1213</v>
+      </c>
+      <c r="AD469" s="2"/>
       <c r="AE469" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF469" t="s" s="2">
-        <v>77</v>
+        <v>1214</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>90</v>
+        <v>1208</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>78</v>
@@ -54854,10 +54866,10 @@
         <v>86</v>
       </c>
       <c r="AJ469" t="s" s="2">
-        <v>77</v>
+        <v>1215</v>
       </c>
       <c r="AK469" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="470">
@@ -54865,12 +54877,14 @@
         <v>995</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1234</v>
+        <v>1216</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1235</v>
-      </c>
-      <c r="D470" s="2"/>
+        <v>1208</v>
+      </c>
+      <c r="D470" t="s" s="2">
+        <v>1217</v>
+      </c>
       <c r="E470" t="s" s="2">
         <v>77</v>
       </c>
@@ -54879,28 +54893,32 @@
         <v>78</v>
       </c>
       <c r="H470" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I470" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J470" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K470" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>92</v>
+        <v>243</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>33</v>
+        <v>1218</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="O470" s="2"/>
-      <c r="P470" s="2"/>
+        <v>1219</v>
+      </c>
+      <c r="O470" t="s" s="2">
+        <v>1211</v>
+      </c>
+      <c r="P470" t="s" s="2">
+        <v>1212</v>
+      </c>
       <c r="Q470" t="s" s="2">
         <v>77</v>
       </c>
@@ -54936,29 +54954,31 @@
         <v>77</v>
       </c>
       <c r="AC470" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD470" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD470" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE470" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF470" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>96</v>
+        <v>1208</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI470" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ470" t="s" s="2">
-        <v>77</v>
+        <v>1215</v>
       </c>
       <c r="AK470" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="471">
@@ -54966,14 +54986,12 @@
         <v>995</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1236</v>
+        <v>1220</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1235</v>
-      </c>
-      <c r="D471" t="s" s="2">
-        <v>1237</v>
-      </c>
+        <v>1221</v>
+      </c>
+      <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
         <v>77</v>
       </c>
@@ -54985,7 +55003,7 @@
         <v>86</v>
       </c>
       <c r="I471" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J471" t="s" s="2">
         <v>77</v>
@@ -54994,17 +55012,15 @@
         <v>77</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>1238</v>
+        <v>87</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1239</v>
+        <v>88</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>1240</v>
-      </c>
-      <c r="O471" t="s" s="2">
-        <v>1241</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O471" s="2"/>
       <c r="P471" s="2"/>
       <c r="Q471" t="s" s="2">
         <v>77</v>
@@ -55053,19 +55069,19 @@
         <v>77</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI471" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ471" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK471" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="472">
@@ -55073,21 +55089,21 @@
         <v>995</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1242</v>
+        <v>1222</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1243</v>
+        <v>1223</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F472" s="2"/>
       <c r="G472" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H472" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I472" t="s" s="2">
         <v>77</v>
@@ -55099,15 +55115,17 @@
         <v>77</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>1226</v>
+        <v>92</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1244</v>
+        <v>112</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="O472" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O472" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P472" s="2"/>
       <c r="Q472" t="s" s="2">
         <v>77</v>
@@ -55144,31 +55162,31 @@
         <v>77</v>
       </c>
       <c r="AC472" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD472" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE472" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF472" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1245</v>
+        <v>96</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI472" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ472" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK472" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="473">
@@ -55176,12 +55194,14 @@
         <v>995</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1246</v>
+        <v>1224</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1247</v>
-      </c>
-      <c r="D473" s="2"/>
+        <v>1223</v>
+      </c>
+      <c r="D473" t="s" s="2">
+        <v>1225</v>
+      </c>
       <c r="E473" t="s" s="2">
         <v>77</v>
       </c>
@@ -55190,36 +55210,34 @@
         <v>78</v>
       </c>
       <c r="H473" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I473" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J473" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K473" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>127</v>
+        <v>1226</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1248</v>
+        <v>1227</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>1249</v>
-      </c>
-      <c r="O473" s="2"/>
-      <c r="P473" t="s" s="2">
-        <v>1250</v>
-      </c>
+        <v>1228</v>
+      </c>
+      <c r="O473" t="s" s="2">
+        <v>1229</v>
+      </c>
+      <c r="P473" s="2"/>
       <c r="Q473" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="R473" t="s" s="2">
-        <v>1251</v>
-      </c>
+      <c r="R473" s="2"/>
       <c r="S473" t="s" s="2">
         <v>77</v>
       </c>
@@ -55239,13 +55257,13 @@
         <v>77</v>
       </c>
       <c r="Y473" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Z473" t="s" s="2">
-        <v>1252</v>
+        <v>77</v>
       </c>
       <c r="AA473" t="s" s="2">
-        <v>1253</v>
+        <v>77</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>77</v>
@@ -55263,19 +55281,19 @@
         <v>77</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1254</v>
+        <v>96</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI473" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ473" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK473" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="474">
@@ -55283,10 +55301,10 @@
         <v>995</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1255</v>
+        <v>1230</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1256</v>
+        <v>1231</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -55309,17 +55327,19 @@
         <v>80</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>87</v>
+        <v>1232</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="O474" s="2"/>
+        <v>1234</v>
+      </c>
+      <c r="O474" t="s" s="2">
+        <v>1235</v>
+      </c>
       <c r="P474" t="s" s="2">
-        <v>1259</v>
+        <v>1236</v>
       </c>
       <c r="Q474" t="s" s="2">
         <v>77</v>
@@ -55368,7 +55388,7 @@
         <v>77</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1260</v>
+        <v>1237</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>78</v>
@@ -55388,10 +55408,10 @@
         <v>995</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1261</v>
+        <v>1238</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1262</v>
+        <v>1239</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -55399,39 +55419,37 @@
       </c>
       <c r="F475" s="2"/>
       <c r="G475" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H475" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I475" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J475" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K475" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L475" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1263</v>
+        <v>900</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1264</v>
+        <v>901</v>
       </c>
       <c r="O475" s="2"/>
-      <c r="P475" t="s" s="2">
-        <v>1265</v>
-      </c>
+      <c r="P475" s="2"/>
       <c r="Q475" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R475" s="2"/>
       <c r="S475" t="s" s="2">
-        <v>1266</v>
+        <v>77</v>
       </c>
       <c r="T475" t="s" s="2">
         <v>77</v>
@@ -55473,7 +55491,7 @@
         <v>77</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1267</v>
+        <v>90</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>78</v>
@@ -55482,10 +55500,10 @@
         <v>86</v>
       </c>
       <c r="AJ475" t="s" s="2">
-        <v>1268</v>
+        <v>77</v>
       </c>
       <c r="AK475" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="476">
@@ -55493,10 +55511,10 @@
         <v>995</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1269</v>
+        <v>1240</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1270</v>
+        <v>1241</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -55504,35 +55522,31 @@
       </c>
       <c r="F476" s="2"/>
       <c r="G476" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H476" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I476" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K476" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L476" t="s" s="2">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1271</v>
+        <v>33</v>
       </c>
       <c r="N476" t="s" s="2">
-        <v>1272</v>
-      </c>
-      <c r="O476" t="s" s="2">
-        <v>1273</v>
-      </c>
-      <c r="P476" t="s" s="2">
-        <v>1274</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O476" s="2"/>
+      <c r="P476" s="2"/>
       <c r="Q476" t="s" s="2">
         <v>77</v>
       </c>
@@ -55568,31 +55582,29 @@
         <v>77</v>
       </c>
       <c r="AC476" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD476" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="AD476" s="2"/>
       <c r="AE476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF476" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1275</v>
+        <v>96</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI476" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK476" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="477">
@@ -55600,13 +55612,13 @@
         <v>995</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1276</v>
+        <v>1242</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1202</v>
+        <v>1241</v>
       </c>
       <c r="D477" t="s" s="2">
-        <v>1277</v>
+        <v>1243</v>
       </c>
       <c r="E477" t="s" s="2">
         <v>77</v>
@@ -55625,23 +55637,21 @@
         <v>77</v>
       </c>
       <c r="K477" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L477" t="s" s="2">
-        <v>422</v>
+        <v>1244</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1212</v>
+        <v>1245</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1213</v>
+        <v>1246</v>
       </c>
       <c r="O477" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="P477" t="s" s="2">
-        <v>1206</v>
-      </c>
+        <v>1247</v>
+      </c>
+      <c r="P477" s="2"/>
       <c r="Q477" t="s" s="2">
         <v>77</v>
       </c>
@@ -55665,11 +55675,13 @@
         <v>77</v>
       </c>
       <c r="Y477" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="Z477" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Z477" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AA477" t="s" s="2">
-        <v>1278</v>
+        <v>77</v>
       </c>
       <c r="AB477" t="s" s="2">
         <v>77</v>
@@ -55687,19 +55699,19 @@
         <v>77</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1202</v>
+        <v>96</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI477" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ477" t="s" s="2">
-        <v>1209</v>
+        <v>83</v>
       </c>
       <c r="AK477" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="478">
@@ -55707,10 +55719,10 @@
         <v>995</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1279</v>
+        <v>1248</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1215</v>
+        <v>1249</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -55733,13 +55745,13 @@
         <v>77</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>87</v>
+        <v>1232</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>88</v>
+        <v>1250</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>89</v>
+        <v>909</v>
       </c>
       <c r="O478" s="2"/>
       <c r="P478" s="2"/>
@@ -55790,7 +55802,7 @@
         <v>77</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>90</v>
+        <v>1251</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>78</v>
@@ -55810,48 +55822,50 @@
         <v>995</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1280</v>
+        <v>1252</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1217</v>
+        <v>1253</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F479" s="2"/>
       <c r="G479" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H479" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I479" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J479" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K479" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>112</v>
+        <v>1254</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O479" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P479" s="2"/>
+        <v>1255</v>
+      </c>
+      <c r="O479" s="2"/>
+      <c r="P479" t="s" s="2">
+        <v>1256</v>
+      </c>
       <c r="Q479" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="R479" s="2"/>
+      <c r="R479" t="s" s="2">
+        <v>1257</v>
+      </c>
       <c r="S479" t="s" s="2">
         <v>77</v>
       </c>
@@ -55871,43 +55885,43 @@
         <v>77</v>
       </c>
       <c r="Y479" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Z479" t="s" s="2">
-        <v>77</v>
+        <v>1258</v>
       </c>
       <c r="AA479" t="s" s="2">
-        <v>77</v>
+        <v>1259</v>
       </c>
       <c r="AB479" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AC479" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD479" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE479" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF479" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>96</v>
+        <v>1260</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI479" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ479" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK479" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="480">
@@ -55915,10 +55929,10 @@
         <v>995</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1281</v>
+        <v>1261</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1282</v>
+        <v>1262</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -55929,7 +55943,7 @@
         <v>86</v>
       </c>
       <c r="H480" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I480" t="s" s="2">
         <v>80</v>
@@ -55941,19 +55955,17 @@
         <v>80</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>437</v>
+        <v>1263</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O480" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>1264</v>
+      </c>
+      <c r="O480" s="2"/>
       <c r="P480" t="s" s="2">
-        <v>440</v>
+        <v>1265</v>
       </c>
       <c r="Q480" t="s" s="2">
         <v>77</v>
@@ -56002,13 +56014,13 @@
         <v>77</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>442</v>
+        <v>1266</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI480" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ480" t="s" s="2">
         <v>77</v>
@@ -56022,10 +56034,10 @@
         <v>995</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1284</v>
+        <v>1268</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56033,37 +56045,39 @@
       </c>
       <c r="F481" s="2"/>
       <c r="G481" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H481" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I481" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J481" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K481" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>88</v>
+        <v>1269</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>89</v>
+        <v>1270</v>
       </c>
       <c r="O481" s="2"/>
-      <c r="P481" s="2"/>
+      <c r="P481" t="s" s="2">
+        <v>1271</v>
+      </c>
       <c r="Q481" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R481" s="2"/>
       <c r="S481" t="s" s="2">
-        <v>77</v>
+        <v>1272</v>
       </c>
       <c r="T481" t="s" s="2">
         <v>77</v>
@@ -56105,7 +56119,7 @@
         <v>77</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>90</v>
+        <v>1273</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>78</v>
@@ -56114,10 +56128,10 @@
         <v>86</v>
       </c>
       <c r="AJ481" t="s" s="2">
-        <v>77</v>
+        <v>1274</v>
       </c>
       <c r="AK481" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="482">
@@ -56125,44 +56139,46 @@
         <v>995</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1285</v>
+        <v>1275</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1286</v>
+        <v>1276</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F482" s="2"/>
       <c r="G482" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H482" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I482" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J482" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K482" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>112</v>
+        <v>1277</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>113</v>
+        <v>1278</v>
       </c>
       <c r="O482" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P482" s="2"/>
+        <v>1279</v>
+      </c>
+      <c r="P482" t="s" s="2">
+        <v>1280</v>
+      </c>
       <c r="Q482" t="s" s="2">
         <v>77</v>
       </c>
@@ -56198,31 +56214,31 @@
         <v>77</v>
       </c>
       <c r="AC482" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD482" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE482" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF482" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>96</v>
+        <v>1281</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI482" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ482" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK482" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="483">
@@ -56230,18 +56246,20 @@
         <v>995</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1288</v>
-      </c>
-      <c r="D483" s="2"/>
+        <v>1208</v>
+      </c>
+      <c r="D483" t="s" s="2">
+        <v>1283</v>
+      </c>
       <c r="E483" t="s" s="2">
         <v>77</v>
       </c>
       <c r="F483" s="2"/>
       <c r="G483" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H483" t="s" s="2">
         <v>86</v>
@@ -56256,19 +56274,19 @@
         <v>80</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>98</v>
+        <v>422</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>116</v>
+        <v>1218</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>117</v>
+        <v>1219</v>
       </c>
       <c r="O483" t="s" s="2">
-        <v>118</v>
+        <v>1211</v>
       </c>
       <c r="P483" t="s" s="2">
-        <v>119</v>
+        <v>1212</v>
       </c>
       <c r="Q483" t="s" s="2">
         <v>77</v>
@@ -56293,13 +56311,11 @@
         <v>77</v>
       </c>
       <c r="Y483" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z483" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Z483" s="2"/>
       <c r="AA483" t="s" s="2">
-        <v>77</v>
+        <v>1284</v>
       </c>
       <c r="AB483" t="s" s="2">
         <v>77</v>
@@ -56317,7 +56333,7 @@
         <v>77</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>120</v>
+        <v>1208</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>78</v>
@@ -56326,7 +56342,7 @@
         <v>86</v>
       </c>
       <c r="AJ483" t="s" s="2">
-        <v>77</v>
+        <v>1215</v>
       </c>
       <c r="AK483" t="s" s="2">
         <v>108</v>
@@ -56337,10 +56353,10 @@
         <v>995</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1290</v>
+        <v>1221</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -56354,26 +56370,24 @@
         <v>86</v>
       </c>
       <c r="I484" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J484" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K484" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L484" t="s" s="2">
         <v>87</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O484" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O484" s="2"/>
       <c r="P484" s="2"/>
       <c r="Q484" t="s" s="2">
         <v>77</v>
@@ -56422,7 +56436,7 @@
         <v>77</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>78</v>
@@ -56434,7 +56448,7 @@
         <v>77</v>
       </c>
       <c r="AK484" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="485">
@@ -56442,44 +56456,44 @@
         <v>995</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1292</v>
+        <v>1223</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F485" s="2"/>
       <c r="G485" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H485" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I485" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J485" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K485" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O485" s="2"/>
-      <c r="P485" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O485" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P485" s="2"/>
       <c r="Q485" t="s" s="2">
         <v>77</v>
       </c>
@@ -56515,31 +56529,31 @@
         <v>77</v>
       </c>
       <c r="AC485" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD485" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE485" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF485" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI485" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ485" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK485" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="486">
@@ -56547,10 +56561,10 @@
         <v>995</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -56558,13 +56572,13 @@
       </c>
       <c r="F486" s="2"/>
       <c r="G486" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H486" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I486" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J486" t="s" s="2">
         <v>77</v>
@@ -56573,17 +56587,19 @@
         <v>80</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>133</v>
+        <v>437</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O486" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O486" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P486" t="s" s="2">
-        <v>135</v>
+        <v>440</v>
       </c>
       <c r="Q486" t="s" s="2">
         <v>77</v>
@@ -56632,13 +56648,13 @@
         <v>77</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>136</v>
+        <v>442</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI486" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ486" t="s" s="2">
         <v>77</v>
@@ -56652,10 +56668,10 @@
         <v>995</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56675,23 +56691,19 @@
         <v>77</v>
       </c>
       <c r="K487" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O487" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="P487" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O487" s="2"/>
+      <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
         <v>77</v>
       </c>
@@ -56739,7 +56751,7 @@
         <v>77</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>78</v>
@@ -56751,7 +56763,7 @@
         <v>77</v>
       </c>
       <c r="AK487" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="488">
@@ -56759,21 +56771,21 @@
         <v>995</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1297</v>
+        <v>1291</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F488" s="2"/>
       <c r="G488" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I488" t="s" s="2">
         <v>77</v>
@@ -56782,23 +56794,21 @@
         <v>77</v>
       </c>
       <c r="K488" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>463</v>
+        <v>112</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>464</v>
+        <v>113</v>
       </c>
       <c r="O488" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P488" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
         <v>77</v>
       </c>
@@ -56834,31 +56844,31 @@
         <v>77</v>
       </c>
       <c r="AC488" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD488" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE488" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF488" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>467</v>
+        <v>96</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK488" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="489">
@@ -56866,20 +56876,18 @@
         <v>995</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1202</v>
-      </c>
-      <c r="D489" t="s" s="2">
-        <v>1300</v>
-      </c>
+        <v>1294</v>
+      </c>
+      <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
         <v>77</v>
       </c>
       <c r="F489" s="2"/>
       <c r="G489" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H489" t="s" s="2">
         <v>86</v>
@@ -56894,19 +56902,19 @@
         <v>80</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>1301</v>
+        <v>98</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1212</v>
+        <v>116</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>1213</v>
+        <v>117</v>
       </c>
       <c r="O489" t="s" s="2">
-        <v>1205</v>
+        <v>118</v>
       </c>
       <c r="P489" t="s" s="2">
-        <v>1206</v>
+        <v>119</v>
       </c>
       <c r="Q489" t="s" s="2">
         <v>77</v>
@@ -56955,7 +56963,7 @@
         <v>77</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1202</v>
+        <v>120</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>78</v>
@@ -56964,7 +56972,7 @@
         <v>86</v>
       </c>
       <c r="AJ489" t="s" s="2">
-        <v>1209</v>
+        <v>77</v>
       </c>
       <c r="AK489" t="s" s="2">
         <v>108</v>
@@ -56975,14 +56983,12 @@
         <v>995</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1302</v>
+        <v>1295</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1202</v>
-      </c>
-      <c r="D490" t="s" s="2">
-        <v>1303</v>
-      </c>
+        <v>1296</v>
+      </c>
+      <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
         <v>77</v>
       </c>
@@ -57003,20 +57009,18 @@
         <v>80</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>1304</v>
+        <v>87</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1212</v>
+        <v>122</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1213</v>
+        <v>123</v>
       </c>
       <c r="O490" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="P490" t="s" s="2">
-        <v>1206</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="P490" s="2"/>
       <c r="Q490" t="s" s="2">
         <v>77</v>
       </c>
@@ -57064,7 +57068,7 @@
         <v>77</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1202</v>
+        <v>125</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>78</v>
@@ -57073,7 +57077,7 @@
         <v>86</v>
       </c>
       <c r="AJ490" t="s" s="2">
-        <v>1209</v>
+        <v>77</v>
       </c>
       <c r="AK490" t="s" s="2">
         <v>108</v>
@@ -57084,10 +57088,10 @@
         <v>995</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1305</v>
+        <v>1298</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57095,7 +57099,7 @@
       </c>
       <c r="F491" s="2"/>
       <c r="G491" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H491" t="s" s="2">
         <v>86</v>
@@ -57107,22 +57111,20 @@
         <v>77</v>
       </c>
       <c r="K491" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>422</v>
+        <v>127</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1306</v>
+        <v>128</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1307</v>
-      </c>
-      <c r="O491" t="s" s="2">
-        <v>1308</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O491" s="2"/>
       <c r="P491" t="s" s="2">
-        <v>1309</v>
+        <v>130</v>
       </c>
       <c r="Q491" t="s" s="2">
         <v>77</v>
@@ -57147,13 +57149,13 @@
         <v>77</v>
       </c>
       <c r="Y491" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z491" t="s" s="2">
-        <v>1310</v>
+        <v>77</v>
       </c>
       <c r="AA491" t="s" s="2">
-        <v>1311</v>
+        <v>77</v>
       </c>
       <c r="AB491" t="s" s="2">
         <v>77</v>
@@ -57171,7 +57173,7 @@
         <v>77</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1305</v>
+        <v>131</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>78</v>
@@ -57180,7 +57182,7 @@
         <v>86</v>
       </c>
       <c r="AJ491" t="s" s="2">
-        <v>1312</v>
+        <v>77</v>
       </c>
       <c r="AK491" t="s" s="2">
         <v>108</v>
@@ -57191,45 +57193,43 @@
         <v>995</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1313</v>
+        <v>1299</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1313</v>
+        <v>1300</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
-        <v>1314</v>
+        <v>77</v>
       </c>
       <c r="F492" s="2"/>
       <c r="G492" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H492" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I492" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J492" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K492" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J492" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K492" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="L492" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1315</v>
+        <v>133</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1316</v>
-      </c>
-      <c r="O492" t="s" s="2">
-        <v>1317</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="O492" s="2"/>
       <c r="P492" t="s" s="2">
-        <v>1318</v>
+        <v>135</v>
       </c>
       <c r="Q492" t="s" s="2">
         <v>77</v>
@@ -57254,13 +57254,13 @@
         <v>77</v>
       </c>
       <c r="Y492" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z492" t="s" s="2">
-        <v>1319</v>
+        <v>77</v>
       </c>
       <c r="AA492" t="s" s="2">
-        <v>1320</v>
+        <v>77</v>
       </c>
       <c r="AB492" t="s" s="2">
         <v>77</v>
@@ -57278,13 +57278,13 @@
         <v>77</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1313</v>
+        <v>136</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI492" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ492" t="s" s="2">
         <v>77</v>
@@ -57298,10 +57298,10 @@
         <v>995</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1321</v>
+        <v>1301</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1321</v>
+        <v>1302</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57312,31 +57312,31 @@
         <v>78</v>
       </c>
       <c r="H493" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I493" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J493" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K493" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J493" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K493" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="L493" t="s" s="2">
-        <v>727</v>
+        <v>138</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1322</v>
+        <v>139</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1323</v>
+        <v>140</v>
       </c>
       <c r="O493" t="s" s="2">
-        <v>1324</v>
+        <v>141</v>
       </c>
       <c r="P493" t="s" s="2">
-        <v>1325</v>
+        <v>142</v>
       </c>
       <c r="Q493" t="s" s="2">
         <v>77</v>
@@ -57385,13 +57385,13 @@
         <v>77</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1321</v>
+        <v>143</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI493" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ493" t="s" s="2">
         <v>77</v>
@@ -57405,10 +57405,10 @@
         <v>995</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1326</v>
+        <v>1303</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1326</v>
+        <v>1304</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57419,7 +57419,7 @@
         <v>78</v>
       </c>
       <c r="H494" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I494" t="s" s="2">
         <v>77</v>
@@ -57428,21 +57428,23 @@
         <v>77</v>
       </c>
       <c r="K494" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1327</v>
+        <v>463</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1328</v>
+        <v>464</v>
       </c>
       <c r="O494" t="s" s="2">
-        <v>1329</v>
-      </c>
-      <c r="P494" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="P494" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="Q494" t="s" s="2">
         <v>77</v>
       </c>
@@ -57466,13 +57468,13 @@
         <v>77</v>
       </c>
       <c r="Y494" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z494" t="s" s="2">
-        <v>724</v>
+        <v>77</v>
       </c>
       <c r="AA494" t="s" s="2">
-        <v>725</v>
+        <v>77</v>
       </c>
       <c r="AB494" t="s" s="2">
         <v>77</v>
@@ -57490,7 +57492,7 @@
         <v>77</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1326</v>
+        <v>467</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>78</v>
@@ -57510,12 +57512,14 @@
         <v>995</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1330</v>
+        <v>1305</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1330</v>
-      </c>
-      <c r="D495" s="2"/>
+        <v>1208</v>
+      </c>
+      <c r="D495" t="s" s="2">
+        <v>1306</v>
+      </c>
       <c r="E495" t="s" s="2">
         <v>77</v>
       </c>
@@ -57533,22 +57537,22 @@
         <v>77</v>
       </c>
       <c r="K495" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>422</v>
+        <v>1307</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1331</v>
+        <v>1218</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1332</v>
+        <v>1219</v>
       </c>
       <c r="O495" t="s" s="2">
-        <v>1333</v>
+        <v>1211</v>
       </c>
       <c r="P495" t="s" s="2">
-        <v>1334</v>
+        <v>1212</v>
       </c>
       <c r="Q495" t="s" s="2">
         <v>77</v>
@@ -57573,13 +57577,13 @@
         <v>77</v>
       </c>
       <c r="Y495" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z495" t="s" s="2">
-        <v>1335</v>
+        <v>77</v>
       </c>
       <c r="AA495" t="s" s="2">
-        <v>1336</v>
+        <v>77</v>
       </c>
       <c r="AB495" t="s" s="2">
         <v>77</v>
@@ -57597,7 +57601,7 @@
         <v>77</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1330</v>
+        <v>1208</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>78</v>
@@ -57606,7 +57610,7 @@
         <v>86</v>
       </c>
       <c r="AJ495" t="s" s="2">
-        <v>77</v>
+        <v>1215</v>
       </c>
       <c r="AK495" t="s" s="2">
         <v>108</v>
@@ -57617,12 +57621,14 @@
         <v>995</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1337</v>
+        <v>1308</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1337</v>
-      </c>
-      <c r="D496" s="2"/>
+        <v>1208</v>
+      </c>
+      <c r="D496" t="s" s="2">
+        <v>1309</v>
+      </c>
       <c r="E496" t="s" s="2">
         <v>77</v>
       </c>
@@ -57634,25 +57640,29 @@
         <v>86</v>
       </c>
       <c r="I496" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J496" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K496" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>87</v>
+        <v>1310</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>88</v>
+        <v>1218</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O496" s="2"/>
-      <c r="P496" s="2"/>
+        <v>1219</v>
+      </c>
+      <c r="O496" t="s" s="2">
+        <v>1211</v>
+      </c>
+      <c r="P496" t="s" s="2">
+        <v>1212</v>
+      </c>
       <c r="Q496" t="s" s="2">
         <v>77</v>
       </c>
@@ -57700,7 +57710,7 @@
         <v>77</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>90</v>
+        <v>1208</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>78</v>
@@ -57709,10 +57719,10 @@
         <v>86</v>
       </c>
       <c r="AJ496" t="s" s="2">
-        <v>77</v>
+        <v>1215</v>
       </c>
       <c r="AK496" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="497">
@@ -57720,24 +57730,24 @@
         <v>995</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1338</v>
+        <v>1311</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1338</v>
+        <v>1311</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F497" s="2"/>
       <c r="G497" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H497" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I497" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J497" t="s" s="2">
         <v>77</v>
@@ -57746,18 +57756,20 @@
         <v>77</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>92</v>
+        <v>422</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>113</v>
+        <v>1313</v>
       </c>
       <c r="O497" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P497" s="2"/>
+        <v>1314</v>
+      </c>
+      <c r="P497" t="s" s="2">
+        <v>1315</v>
+      </c>
       <c r="Q497" t="s" s="2">
         <v>77</v>
       </c>
@@ -57781,43 +57793,43 @@
         <v>77</v>
       </c>
       <c r="Y497" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z497" t="s" s="2">
-        <v>77</v>
+        <v>1316</v>
       </c>
       <c r="AA497" t="s" s="2">
-        <v>77</v>
+        <v>1317</v>
       </c>
       <c r="AB497" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AC497" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD497" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE497" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF497" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>96</v>
+        <v>1311</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI497" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ497" t="s" s="2">
-        <v>77</v>
+        <v>1318</v>
       </c>
       <c r="AK497" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="498">
@@ -57825,14 +57837,14 @@
         <v>995</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1339</v>
+        <v>1319</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1339</v>
+        <v>1319</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
-        <v>77</v>
+        <v>1320</v>
       </c>
       <c r="F498" s="2"/>
       <c r="G498" t="s" s="2">
@@ -57848,22 +57860,22 @@
         <v>77</v>
       </c>
       <c r="K498" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>103</v>
+        <v>422</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>437</v>
+        <v>1321</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>438</v>
+        <v>1322</v>
       </c>
       <c r="O498" t="s" s="2">
-        <v>439</v>
+        <v>1323</v>
       </c>
       <c r="P498" t="s" s="2">
-        <v>440</v>
+        <v>1324</v>
       </c>
       <c r="Q498" t="s" s="2">
         <v>77</v>
@@ -57888,13 +57900,13 @@
         <v>77</v>
       </c>
       <c r="Y498" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z498" t="s" s="2">
-        <v>77</v>
+        <v>1325</v>
       </c>
       <c r="AA498" t="s" s="2">
-        <v>77</v>
+        <v>1326</v>
       </c>
       <c r="AB498" t="s" s="2">
         <v>77</v>
@@ -57912,7 +57924,7 @@
         <v>77</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>442</v>
+        <v>1319</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>78</v>
@@ -57932,10 +57944,10 @@
         <v>995</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -57946,10 +57958,10 @@
         <v>78</v>
       </c>
       <c r="H499" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I499" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J499" t="s" s="2">
         <v>77</v>
@@ -57958,16 +57970,20 @@
         <v>77</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>87</v>
+        <v>727</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>88</v>
+        <v>1328</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O499" s="2"/>
-      <c r="P499" s="2"/>
+        <v>1329</v>
+      </c>
+      <c r="O499" t="s" s="2">
+        <v>1330</v>
+      </c>
+      <c r="P499" t="s" s="2">
+        <v>1331</v>
+      </c>
       <c r="Q499" t="s" s="2">
         <v>77</v>
       </c>
@@ -58015,19 +58031,19 @@
         <v>77</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>90</v>
+        <v>1327</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI499" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ499" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK499" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="500">
@@ -58035,21 +58051,21 @@
         <v>995</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1341</v>
+        <v>1332</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1341</v>
+        <v>1332</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H500" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I500" t="s" s="2">
         <v>77</v>
@@ -58061,16 +58077,16 @@
         <v>77</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>92</v>
+        <v>422</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>112</v>
+        <v>1333</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>113</v>
+        <v>1334</v>
       </c>
       <c r="O500" t="s" s="2">
-        <v>114</v>
+        <v>1335</v>
       </c>
       <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
@@ -58096,43 +58112,43 @@
         <v>77</v>
       </c>
       <c r="Y500" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z500" t="s" s="2">
-        <v>77</v>
+        <v>724</v>
       </c>
       <c r="AA500" t="s" s="2">
-        <v>77</v>
+        <v>725</v>
       </c>
       <c r="AB500" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AC500" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD500" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE500" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF500" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>96</v>
+        <v>1332</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI500" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ500" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK500" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="501">
@@ -58140,10 +58156,10 @@
         <v>995</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -58151,7 +58167,7 @@
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H501" t="s" s="2">
         <v>86</v>
@@ -58163,22 +58179,22 @@
         <v>77</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>98</v>
+        <v>422</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>116</v>
+        <v>1337</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>117</v>
+        <v>1338</v>
       </c>
       <c r="O501" t="s" s="2">
-        <v>118</v>
+        <v>1339</v>
       </c>
       <c r="P501" t="s" s="2">
-        <v>119</v>
+        <v>1340</v>
       </c>
       <c r="Q501" t="s" s="2">
         <v>77</v>
@@ -58203,13 +58219,13 @@
         <v>77</v>
       </c>
       <c r="Y501" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z501" t="s" s="2">
-        <v>77</v>
+        <v>1341</v>
       </c>
       <c r="AA501" t="s" s="2">
-        <v>77</v>
+        <v>1342</v>
       </c>
       <c r="AB501" t="s" s="2">
         <v>77</v>
@@ -58227,7 +58243,7 @@
         <v>77</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>120</v>
+        <v>1336</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>78</v>
@@ -58270,20 +58286,18 @@
         <v>77</v>
       </c>
       <c r="K502" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L502" t="s" s="2">
         <v>87</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O502" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O502" s="2"/>
       <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
         <v>77</v>
@@ -58332,7 +58346,7 @@
         <v>77</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>78</v>
@@ -58344,7 +58358,7 @@
         <v>77</v>
       </c>
       <c r="AK502" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="503">
@@ -58359,37 +58373,37 @@
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F503" s="2"/>
       <c r="G503" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I503" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J503" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K503" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O503" s="2"/>
-      <c r="P503" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O503" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P503" s="2"/>
       <c r="Q503" t="s" s="2">
         <v>77</v>
       </c>
@@ -58425,31 +58439,31 @@
         <v>77</v>
       </c>
       <c r="AC503" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD503" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE503" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF503" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ503" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK503" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="504">
@@ -58471,7 +58485,7 @@
         <v>78</v>
       </c>
       <c r="H504" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I504" t="s" s="2">
         <v>80</v>
@@ -58483,17 +58497,19 @@
         <v>80</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>133</v>
+        <v>437</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O504" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O504" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P504" t="s" s="2">
-        <v>135</v>
+        <v>440</v>
       </c>
       <c r="Q504" t="s" s="2">
         <v>77</v>
@@ -58542,13 +58558,13 @@
         <v>77</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>136</v>
+        <v>442</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI504" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ504" t="s" s="2">
         <v>77</v>
@@ -58585,23 +58601,19 @@
         <v>77</v>
       </c>
       <c r="K505" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O505" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="P505" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O505" s="2"/>
+      <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
         <v>77</v>
       </c>
@@ -58649,7 +58661,7 @@
         <v>77</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>78</v>
@@ -58661,7 +58673,7 @@
         <v>77</v>
       </c>
       <c r="AK505" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="506">
@@ -58676,14 +58688,14 @@
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H506" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I506" t="s" s="2">
         <v>77</v>
@@ -58692,23 +58704,21 @@
         <v>77</v>
       </c>
       <c r="K506" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>463</v>
+        <v>112</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>464</v>
+        <v>113</v>
       </c>
       <c r="O506" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P506" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
         <v>77</v>
       </c>
@@ -58744,31 +58754,31 @@
         <v>77</v>
       </c>
       <c r="AC506" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD506" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE506" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF506" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>467</v>
+        <v>96</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI506" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ506" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK506" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="507">
@@ -58787,7 +58797,7 @@
       </c>
       <c r="F507" s="2"/>
       <c r="G507" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H507" t="s" s="2">
         <v>86</v>
@@ -58799,21 +58809,23 @@
         <v>77</v>
       </c>
       <c r="K507" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>708</v>
+        <v>98</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>709</v>
+        <v>116</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="O507" t="s" s="2">
-        <v>1349</v>
-      </c>
-      <c r="P507" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="P507" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="Q507" t="s" s="2">
         <v>77</v>
       </c>
@@ -58861,7 +58873,7 @@
         <v>77</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1348</v>
+        <v>120</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>78</v>
@@ -58881,10 +58893,10 @@
         <v>995</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -58904,18 +58916,20 @@
         <v>77</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L508" t="s" s="2">
         <v>87</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O508" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="O508" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
         <v>77</v>
@@ -58964,7 +58978,7 @@
         <v>77</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>78</v>
@@ -58976,7 +58990,7 @@
         <v>77</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="509">
@@ -58984,44 +58998,44 @@
         <v>995</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F509" s="2"/>
       <c r="G509" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H509" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I509" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J509" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K509" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O509" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P509" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="O509" s="2"/>
+      <c r="P509" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="Q509" t="s" s="2">
         <v>77</v>
       </c>
@@ -59057,31 +59071,31 @@
         <v>77</v>
       </c>
       <c r="AC509" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD509" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE509" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF509" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI509" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ509" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK509" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="510">
@@ -59089,10 +59103,10 @@
         <v>995</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59118,15 +59132,15 @@
         <v>87</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>611</v>
+        <v>133</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O510" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="P510" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="O510" s="2"/>
+      <c r="P510" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="Q510" t="s" s="2">
         <v>77</v>
       </c>
@@ -59174,7 +59188,7 @@
         <v>77</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>614</v>
+        <v>136</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>78</v>
@@ -59183,7 +59197,7 @@
         <v>86</v>
       </c>
       <c r="AJ510" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AK510" t="s" s="2">
         <v>108</v>
@@ -59194,10 +59208,10 @@
         <v>995</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59220,18 +59234,20 @@
         <v>80</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>617</v>
+        <v>139</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>618</v>
+        <v>140</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="P511" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="P511" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="Q511" t="s" s="2">
         <v>77</v>
       </c>
@@ -59255,13 +59271,13 @@
         <v>77</v>
       </c>
       <c r="Y511" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z511" t="s" s="2">
-        <v>620</v>
+        <v>77</v>
       </c>
       <c r="AA511" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AB511" t="s" s="2">
         <v>77</v>
@@ -59279,7 +59295,7 @@
         <v>77</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>622</v>
+        <v>143</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>78</v>
@@ -59299,10 +59315,10 @@
         <v>995</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59316,7 +59332,7 @@
         <v>86</v>
       </c>
       <c r="I512" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J512" t="s" s="2">
         <v>77</v>
@@ -59325,18 +59341,20 @@
         <v>80</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>624</v>
+        <v>463</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>625</v>
+        <v>464</v>
       </c>
       <c r="O512" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="P512" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="P512" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="Q512" t="s" s="2">
         <v>77</v>
       </c>
@@ -59384,7 +59402,7 @@
         <v>77</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>627</v>
+        <v>467</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>78</v>
@@ -59404,10 +59422,10 @@
         <v>995</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59421,25 +59439,25 @@
         <v>86</v>
       </c>
       <c r="I513" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J513" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K513" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>87</v>
+        <v>708</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>629</v>
+        <v>709</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>630</v>
+        <v>179</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>631</v>
+        <v>1355</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -59489,7 +59507,7 @@
         <v>77</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>632</v>
+        <v>1354</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>78</v>
@@ -59526,7 +59544,7 @@
         <v>86</v>
       </c>
       <c r="I514" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J514" t="s" s="2">
         <v>77</v>
@@ -59535,17 +59553,15 @@
         <v>77</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>1357</v>
+        <v>87</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>1358</v>
+        <v>88</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>1359</v>
-      </c>
-      <c r="O514" t="s" s="2">
-        <v>1360</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O514" s="2"/>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
         <v>77</v>
@@ -59594,7 +59610,7 @@
         <v>77</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1356</v>
+        <v>90</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>78</v>
@@ -59606,7 +59622,7 @@
         <v>77</v>
       </c>
       <c r="AK514" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="515">
@@ -59614,21 +59630,21 @@
         <v>995</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F515" s="2"/>
       <c r="G515" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H515" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I515" t="s" s="2">
         <v>77</v>
@@ -59640,15 +59656,17 @@
         <v>77</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O515" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O515" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P515" s="2"/>
       <c r="Q515" t="s" s="2">
         <v>77</v>
@@ -59685,31 +59703,31 @@
         <v>77</v>
       </c>
       <c r="AC515" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD515" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE515" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF515" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI515" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ515" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK515" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="516">
@@ -59717,42 +59735,42 @@
         <v>995</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F516" s="2"/>
       <c r="G516" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H516" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I516" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J516" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K516" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>112</v>
+        <v>611</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>113</v>
+        <v>612</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
@@ -59790,31 +59808,31 @@
         <v>77</v>
       </c>
       <c r="AC516" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD516" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE516" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF516" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>96</v>
+        <v>614</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI516" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ516" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK516" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="517">
@@ -59822,10 +59840,10 @@
         <v>995</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -59839,7 +59857,7 @@
         <v>86</v>
       </c>
       <c r="I517" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J517" t="s" s="2">
         <v>77</v>
@@ -59848,16 +59866,16 @@
         <v>80</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="O517" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
@@ -59883,13 +59901,13 @@
         <v>77</v>
       </c>
       <c r="Y517" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z517" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA517" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB517" t="s" s="2">
         <v>77</v>
@@ -59907,7 +59925,7 @@
         <v>77</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>78</v>
@@ -59916,7 +59934,7 @@
         <v>86</v>
       </c>
       <c r="AJ517" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AK517" t="s" s="2">
         <v>108</v>
@@ -59927,10 +59945,10 @@
         <v>995</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -59944,7 +59962,7 @@
         <v>86</v>
       </c>
       <c r="I518" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J518" t="s" s="2">
         <v>77</v>
@@ -59953,16 +59971,16 @@
         <v>80</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="O518" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
@@ -59988,13 +60006,13 @@
         <v>77</v>
       </c>
       <c r="Y518" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z518" t="s" s="2">
-        <v>620</v>
+        <v>77</v>
       </c>
       <c r="AA518" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AB518" t="s" s="2">
         <v>77</v>
@@ -60012,7 +60030,7 @@
         <v>77</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>78</v>
@@ -60032,10 +60050,10 @@
         <v>995</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60049,7 +60067,7 @@
         <v>86</v>
       </c>
       <c r="I519" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J519" t="s" s="2">
         <v>77</v>
@@ -60058,16 +60076,16 @@
         <v>80</v>
       </c>
       <c r="L519" t="s" s="2">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60117,7 +60135,7 @@
         <v>77</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>78</v>
@@ -60137,10 +60155,10 @@
         <v>995</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60154,25 +60172,25 @@
         <v>86</v>
       </c>
       <c r="I520" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J520" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K520" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>87</v>
+        <v>1363</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>629</v>
+        <v>1364</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>630</v>
+        <v>1365</v>
       </c>
       <c r="O520" t="s" s="2">
-        <v>631</v>
+        <v>1366</v>
       </c>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
@@ -60222,7 +60240,7 @@
         <v>77</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>632</v>
+        <v>1362</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>78</v>
@@ -60256,10 +60274,10 @@
         <v>78</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I521" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J521" t="s" s="2">
         <v>77</v>
@@ -60268,20 +60286,16 @@
         <v>77</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1368</v>
+        <v>88</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1369</v>
-      </c>
-      <c r="O521" t="s" s="2">
-        <v>1370</v>
-      </c>
-      <c r="P521" t="s" s="2">
-        <v>1371</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O521" s="2"/>
+      <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
         <v>77</v>
       </c>
@@ -60329,19 +60343,19 @@
         <v>77</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1367</v>
+        <v>90</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI521" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ521" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK521" t="s" s="2">
-        <v>1372</v>
+        <v>77</v>
       </c>
     </row>
     <row r="522">
@@ -60349,21 +60363,21 @@
         <v>995</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F522" s="2"/>
       <c r="G522" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H522" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I522" t="s" s="2">
         <v>77</v>
@@ -60375,15 +60389,17 @@
         <v>77</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O522" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O522" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
         <v>77</v>
@@ -60420,31 +60436,31 @@
         <v>77</v>
       </c>
       <c r="AC522" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD522" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE522" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF522" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI522" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ522" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK522" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="523">
@@ -60452,42 +60468,42 @@
         <v>995</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F523" s="2"/>
       <c r="G523" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H523" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I523" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J523" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K523" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>112</v>
+        <v>611</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>113</v>
+        <v>612</v>
       </c>
       <c r="O523" t="s" s="2">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="P523" s="2"/>
       <c r="Q523" t="s" s="2">
@@ -60537,19 +60553,19 @@
         <v>77</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>96</v>
+        <v>614</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI523" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ523" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK523" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="524">
@@ -60557,46 +60573,44 @@
         <v>995</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="F524" s="2"/>
       <c r="G524" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H524" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I524" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J524" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K524" t="s" s="2">
         <v>80</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>184</v>
+        <v>617</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>185</v>
+        <v>618</v>
       </c>
       <c r="O524" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P524" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
         <v>77</v>
       </c>
@@ -60620,13 +60634,13 @@
         <v>77</v>
       </c>
       <c r="Y524" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z524" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA524" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB524" t="s" s="2">
         <v>77</v>
@@ -60644,19 +60658,19 @@
         <v>77</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>187</v>
+        <v>622</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI524" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ524" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK524" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="525">
@@ -60664,10 +60678,10 @@
         <v>995</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -60687,18 +60701,20 @@
         <v>77</v>
       </c>
       <c r="K525" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>1377</v>
+        <v>167</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1378</v>
+        <v>624</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>1379</v>
-      </c>
-      <c r="O525" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O525" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
         <v>77</v>
@@ -60747,7 +60763,7 @@
         <v>77</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1376</v>
+        <v>627</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>78</v>
@@ -60756,7 +60772,7 @@
         <v>86</v>
       </c>
       <c r="AJ525" t="s" s="2">
-        <v>1380</v>
+        <v>77</v>
       </c>
       <c r="AK525" t="s" s="2">
         <v>108</v>
@@ -60767,10 +60783,10 @@
         <v>995</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1381</v>
+        <v>1372</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1381</v>
+        <v>1372</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -60784,24 +60800,26 @@
         <v>86</v>
       </c>
       <c r="I526" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J526" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K526" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J526" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K526" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="L526" t="s" s="2">
-        <v>1377</v>
+        <v>87</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1382</v>
+        <v>629</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1383</v>
-      </c>
-      <c r="O526" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="O526" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
         <v>77</v>
@@ -60850,7 +60868,7 @@
         <v>77</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1381</v>
+        <v>632</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>78</v>
@@ -60859,7 +60877,7 @@
         <v>86</v>
       </c>
       <c r="AJ526" t="s" s="2">
-        <v>1380</v>
+        <v>77</v>
       </c>
       <c r="AK526" t="s" s="2">
         <v>108</v>
@@ -60870,10 +60888,10 @@
         <v>995</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -60884,10 +60902,10 @@
         <v>78</v>
       </c>
       <c r="H527" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I527" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J527" t="s" s="2">
         <v>77</v>
@@ -60896,19 +60914,19 @@
         <v>77</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>422</v>
+        <v>178</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1385</v>
+        <v>1374</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1386</v>
+        <v>1375</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>1387</v>
+        <v>1376</v>
       </c>
       <c r="P527" t="s" s="2">
-        <v>1388</v>
+        <v>1377</v>
       </c>
       <c r="Q527" t="s" s="2">
         <v>77</v>
@@ -60933,13 +60951,13 @@
         <v>77</v>
       </c>
       <c r="Y527" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="Z527" t="s" s="2">
-        <v>1389</v>
+        <v>77</v>
       </c>
       <c r="AA527" t="s" s="2">
-        <v>1390</v>
+        <v>77</v>
       </c>
       <c r="AB527" t="s" s="2">
         <v>77</v>
@@ -60957,19 +60975,19 @@
         <v>77</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI527" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ527" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK527" t="s" s="2">
-        <v>108</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="528">
@@ -60977,10 +60995,10 @@
         <v>995</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1391</v>
+        <v>1379</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1391</v>
+        <v>1379</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -60991,7 +61009,7 @@
         <v>78</v>
       </c>
       <c r="H528" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I528" t="s" s="2">
         <v>77</v>
@@ -61003,20 +61021,16 @@
         <v>77</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1392</v>
+        <v>88</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1393</v>
-      </c>
-      <c r="O528" t="s" s="2">
-        <v>1394</v>
-      </c>
-      <c r="P528" t="s" s="2">
-        <v>1395</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O528" s="2"/>
+      <c r="P528" s="2"/>
       <c r="Q528" t="s" s="2">
         <v>77</v>
       </c>
@@ -61040,13 +61054,13 @@
         <v>77</v>
       </c>
       <c r="Y528" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z528" t="s" s="2">
-        <v>1396</v>
+        <v>77</v>
       </c>
       <c r="AA528" t="s" s="2">
-        <v>1397</v>
+        <v>77</v>
       </c>
       <c r="AB528" t="s" s="2">
         <v>77</v>
@@ -61064,19 +61078,19 @@
         <v>77</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1391</v>
+        <v>90</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI528" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ528" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK528" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="529">
@@ -61084,21 +61098,21 @@
         <v>995</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F529" s="2"/>
       <c r="G529" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H529" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I529" t="s" s="2">
         <v>77</v>
@@ -61110,18 +61124,18 @@
         <v>77</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>1301</v>
+        <v>92</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1399</v>
+        <v>112</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1400</v>
-      </c>
-      <c r="O529" s="2"/>
-      <c r="P529" t="s" s="2">
-        <v>1401</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O529" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P529" s="2"/>
       <c r="Q529" t="s" s="2">
         <v>77</v>
       </c>
@@ -61169,19 +61183,19 @@
         <v>77</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1398</v>
+        <v>96</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI529" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ529" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK529" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="530">
@@ -61189,42 +61203,46 @@
         <v>995</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1402</v>
+        <v>1381</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1402</v>
+        <v>1381</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="F530" s="2"/>
       <c r="G530" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I530" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J530" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K530" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1403</v>
+        <v>184</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1404</v>
-      </c>
-      <c r="O530" s="2"/>
-      <c r="P530" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="O530" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P530" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Q530" t="s" s="2">
         <v>77</v>
       </c>
@@ -61272,19 +61290,19 @@
         <v>77</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1402</v>
+        <v>187</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ530" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK530" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="531">
@@ -61292,10 +61310,10 @@
         <v>995</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1405</v>
+        <v>1382</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1405</v>
+        <v>1382</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61306,29 +61324,27 @@
         <v>78</v>
       </c>
       <c r="H531" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I531" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J531" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K531" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>1406</v>
+        <v>1383</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1407</v>
+        <v>1384</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1408</v>
-      </c>
-      <c r="O531" t="s" s="2">
-        <v>1409</v>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="O531" s="2"/>
       <c r="P531" s="2"/>
       <c r="Q531" t="s" s="2">
         <v>77</v>
@@ -61377,16 +61393,16 @@
         <v>77</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1405</v>
+        <v>1382</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI531" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ531" t="s" s="2">
-        <v>77</v>
+        <v>1386</v>
       </c>
       <c r="AK531" t="s" s="2">
         <v>108</v>
@@ -61397,10 +61413,10 @@
         <v>995</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1410</v>
+        <v>1387</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1410</v>
+        <v>1387</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61411,29 +61427,27 @@
         <v>78</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I532" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J532" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K532" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>1411</v>
+        <v>1383</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1412</v>
+        <v>1388</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1413</v>
-      </c>
-      <c r="O532" t="s" s="2">
-        <v>1414</v>
-      </c>
+        <v>1389</v>
+      </c>
+      <c r="O532" s="2"/>
       <c r="P532" s="2"/>
       <c r="Q532" t="s" s="2">
         <v>77</v>
@@ -61482,16 +61496,16 @@
         <v>77</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1410</v>
+        <v>1387</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI532" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ532" t="s" s="2">
-        <v>77</v>
+        <v>1386</v>
       </c>
       <c r="AK532" t="s" s="2">
         <v>108</v>
@@ -61502,10 +61516,10 @@
         <v>995</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1415</v>
+        <v>1390</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1415</v>
+        <v>1390</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61516,7 +61530,7 @@
         <v>78</v>
       </c>
       <c r="H533" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I533" t="s" s="2">
         <v>77</v>
@@ -61525,22 +61539,22 @@
         <v>77</v>
       </c>
       <c r="K533" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>178</v>
+        <v>422</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1416</v>
+        <v>1391</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1417</v>
+        <v>1392</v>
       </c>
       <c r="O533" t="s" s="2">
-        <v>1418</v>
+        <v>1393</v>
       </c>
       <c r="P533" t="s" s="2">
-        <v>1419</v>
+        <v>1394</v>
       </c>
       <c r="Q533" t="s" s="2">
         <v>77</v>
@@ -61565,13 +61579,13 @@
         <v>77</v>
       </c>
       <c r="Y533" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="Z533" t="s" s="2">
-        <v>77</v>
+        <v>1395</v>
       </c>
       <c r="AA533" t="s" s="2">
-        <v>77</v>
+        <v>1396</v>
       </c>
       <c r="AB533" t="s" s="2">
         <v>77</v>
@@ -61589,13 +61603,13 @@
         <v>77</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1415</v>
+        <v>1390</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI533" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ533" t="s" s="2">
         <v>77</v>
@@ -61609,10 +61623,10 @@
         <v>995</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1420</v>
+        <v>1397</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1420</v>
+        <v>1397</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61623,7 +61637,7 @@
         <v>78</v>
       </c>
       <c r="H534" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I534" t="s" s="2">
         <v>77</v>
@@ -61635,16 +61649,20 @@
         <v>77</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>87</v>
+        <v>422</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>88</v>
+        <v>1398</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O534" s="2"/>
-      <c r="P534" s="2"/>
+        <v>1399</v>
+      </c>
+      <c r="O534" t="s" s="2">
+        <v>1400</v>
+      </c>
+      <c r="P534" t="s" s="2">
+        <v>1401</v>
+      </c>
       <c r="Q534" t="s" s="2">
         <v>77</v>
       </c>
@@ -61668,13 +61686,13 @@
         <v>77</v>
       </c>
       <c r="Y534" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z534" t="s" s="2">
-        <v>77</v>
+        <v>1402</v>
       </c>
       <c r="AA534" t="s" s="2">
-        <v>77</v>
+        <v>1403</v>
       </c>
       <c r="AB534" t="s" s="2">
         <v>77</v>
@@ -61692,19 +61710,19 @@
         <v>77</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>90</v>
+        <v>1397</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI534" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ534" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK534" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="535">
@@ -61712,21 +61730,21 @@
         <v>995</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1421</v>
+        <v>1404</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1421</v>
+        <v>1404</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F535" s="2"/>
       <c r="G535" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H535" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I535" t="s" s="2">
         <v>77</v>
@@ -61738,18 +61756,18 @@
         <v>77</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>92</v>
+        <v>1307</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>112</v>
+        <v>1405</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P535" s="2"/>
+        <v>1406</v>
+      </c>
+      <c r="O535" s="2"/>
+      <c r="P535" t="s" s="2">
+        <v>1407</v>
+      </c>
       <c r="Q535" t="s" s="2">
         <v>77</v>
       </c>
@@ -61797,19 +61815,19 @@
         <v>77</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>96</v>
+        <v>1404</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI535" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ535" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK535" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="536">
@@ -61817,46 +61835,42 @@
         <v>995</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="F536" s="2"/>
       <c r="G536" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H536" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I536" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J536" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K536" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>184</v>
+        <v>1409</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O536" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P536" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>1410</v>
+      </c>
+      <c r="O536" s="2"/>
+      <c r="P536" s="2"/>
       <c r="Q536" t="s" s="2">
         <v>77</v>
       </c>
@@ -61904,19 +61918,19 @@
         <v>77</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>187</v>
+        <v>1408</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI536" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ536" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK536" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="537">
@@ -61924,10 +61938,10 @@
         <v>995</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1423</v>
+        <v>1411</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1423</v>
+        <v>1411</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -61935,10 +61949,10 @@
       </c>
       <c r="F537" s="2"/>
       <c r="G537" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H537" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I537" t="s" s="2">
         <v>77</v>
@@ -61950,20 +61964,18 @@
         <v>80</v>
       </c>
       <c r="L537" t="s" s="2">
-        <v>422</v>
+        <v>1412</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1424</v>
+        <v>1413</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1425</v>
+        <v>1414</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>1426</v>
-      </c>
-      <c r="P537" t="s" s="2">
-        <v>1133</v>
-      </c>
+        <v>1415</v>
+      </c>
+      <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
         <v>77</v>
       </c>
@@ -61987,13 +61999,13 @@
         <v>77</v>
       </c>
       <c r="Y537" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z537" t="s" s="2">
-        <v>1134</v>
+        <v>77</v>
       </c>
       <c r="AA537" t="s" s="2">
-        <v>1135</v>
+        <v>77</v>
       </c>
       <c r="AB537" t="s" s="2">
         <v>77</v>
@@ -62011,13 +62023,13 @@
         <v>77</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1423</v>
+        <v>1411</v>
       </c>
       <c r="AH537" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI537" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ537" t="s" s="2">
         <v>77</v>
@@ -62031,10 +62043,10 @@
         <v>995</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1427</v>
+        <v>1416</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1427</v>
+        <v>1416</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62045,7 +62057,7 @@
         <v>78</v>
       </c>
       <c r="H538" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I538" t="s" s="2">
         <v>77</v>
@@ -62057,20 +62069,18 @@
         <v>80</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>1428</v>
+        <v>1417</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1429</v>
+        <v>1418</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1213</v>
+        <v>1419</v>
       </c>
       <c r="O538" t="s" s="2">
-        <v>1430</v>
-      </c>
-      <c r="P538" t="s" s="2">
-        <v>1206</v>
-      </c>
+        <v>1420</v>
+      </c>
+      <c r="P538" s="2"/>
       <c r="Q538" t="s" s="2">
         <v>77</v>
       </c>
@@ -62118,13 +62128,13 @@
         <v>77</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1427</v>
+        <v>1416</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI538" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ538" t="s" s="2">
         <v>77</v>
@@ -62138,10 +62148,10 @@
         <v>995</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62152,7 +62162,7 @@
         <v>78</v>
       </c>
       <c r="H539" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I539" t="s" s="2">
         <v>77</v>
@@ -62161,22 +62171,22 @@
         <v>77</v>
       </c>
       <c r="K539" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>422</v>
+        <v>178</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="O539" t="s" s="2">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="P539" t="s" s="2">
-        <v>1309</v>
+        <v>1425</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>77</v>
@@ -62201,13 +62211,13 @@
         <v>77</v>
       </c>
       <c r="Y539" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z539" t="s" s="2">
-        <v>1310</v>
+        <v>77</v>
       </c>
       <c r="AA539" t="s" s="2">
-        <v>1311</v>
+        <v>77</v>
       </c>
       <c r="AB539" t="s" s="2">
         <v>77</v>
@@ -62225,16 +62235,16 @@
         <v>77</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI539" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ539" t="s" s="2">
-        <v>1312</v>
+        <v>77</v>
       </c>
       <c r="AK539" t="s" s="2">
         <v>108</v>
@@ -62245,21 +62255,21 @@
         <v>995</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
-        <v>1314</v>
+        <v>77</v>
       </c>
       <c r="F540" s="2"/>
       <c r="G540" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H540" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I540" t="s" s="2">
         <v>77</v>
@@ -62271,20 +62281,16 @@
         <v>77</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1436</v>
+        <v>88</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1437</v>
-      </c>
-      <c r="O540" t="s" s="2">
-        <v>1317</v>
-      </c>
-      <c r="P540" t="s" s="2">
-        <v>1318</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O540" s="2"/>
+      <c r="P540" s="2"/>
       <c r="Q540" t="s" s="2">
         <v>77</v>
       </c>
@@ -62308,13 +62314,13 @@
         <v>77</v>
       </c>
       <c r="Y540" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z540" t="s" s="2">
-        <v>1438</v>
+        <v>77</v>
       </c>
       <c r="AA540" t="s" s="2">
-        <v>1439</v>
+        <v>77</v>
       </c>
       <c r="AB540" t="s" s="2">
         <v>77</v>
@@ -62332,19 +62338,19 @@
         <v>77</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1435</v>
+        <v>90</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI540" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ540" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK540" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="541">
@@ -62352,14 +62358,14 @@
         <v>995</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1440</v>
+        <v>1427</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1440</v>
+        <v>1427</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F541" s="2"/>
       <c r="G541" t="s" s="2">
@@ -62378,20 +62384,18 @@
         <v>77</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>1441</v>
+        <v>112</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>1442</v>
+        <v>113</v>
       </c>
       <c r="O541" t="s" s="2">
-        <v>1370</v>
-      </c>
-      <c r="P541" t="s" s="2">
-        <v>1371</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
         <v>77</v>
       </c>
@@ -62439,7 +62443,7 @@
         <v>77</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1440</v>
+        <v>96</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>78</v>
@@ -62451,6 +62455,648 @@
         <v>77</v>
       </c>
       <c r="AK541" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B542" t="s" s="2">
+        <v>1428</v>
+      </c>
+      <c r="C542" t="s" s="2">
+        <v>1428</v>
+      </c>
+      <c r="D542" s="2"/>
+      <c r="E542" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F542" s="2"/>
+      <c r="G542" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H542" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J542" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K542" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L542" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M542" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N542" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O542" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P542" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Q542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R542" s="2"/>
+      <c r="S542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG542" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AH542" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI542" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ542" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK542" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B543" t="s" s="2">
+        <v>1429</v>
+      </c>
+      <c r="C543" t="s" s="2">
+        <v>1429</v>
+      </c>
+      <c r="D543" s="2"/>
+      <c r="E543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F543" s="2"/>
+      <c r="G543" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H543" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K543" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L543" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M543" t="s" s="2">
+        <v>1430</v>
+      </c>
+      <c r="N543" t="s" s="2">
+        <v>1431</v>
+      </c>
+      <c r="O543" t="s" s="2">
+        <v>1432</v>
+      </c>
+      <c r="P543" t="s" s="2">
+        <v>1133</v>
+      </c>
+      <c r="Q543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R543" s="2"/>
+      <c r="S543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y543" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z543" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="AA543" t="s" s="2">
+        <v>1135</v>
+      </c>
+      <c r="AB543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG543" t="s" s="2">
+        <v>1429</v>
+      </c>
+      <c r="AH543" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI543" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AJ543" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK543" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B544" t="s" s="2">
+        <v>1433</v>
+      </c>
+      <c r="C544" t="s" s="2">
+        <v>1433</v>
+      </c>
+      <c r="D544" s="2"/>
+      <c r="E544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F544" s="2"/>
+      <c r="G544" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H544" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K544" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L544" t="s" s="2">
+        <v>1434</v>
+      </c>
+      <c r="M544" t="s" s="2">
+        <v>1435</v>
+      </c>
+      <c r="N544" t="s" s="2">
+        <v>1219</v>
+      </c>
+      <c r="O544" t="s" s="2">
+        <v>1436</v>
+      </c>
+      <c r="P544" t="s" s="2">
+        <v>1212</v>
+      </c>
+      <c r="Q544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R544" s="2"/>
+      <c r="S544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG544" t="s" s="2">
+        <v>1433</v>
+      </c>
+      <c r="AH544" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI544" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AJ544" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK544" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B545" t="s" s="2">
+        <v>1437</v>
+      </c>
+      <c r="C545" t="s" s="2">
+        <v>1437</v>
+      </c>
+      <c r="D545" s="2"/>
+      <c r="E545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F545" s="2"/>
+      <c r="G545" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H545" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L545" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M545" t="s" s="2">
+        <v>1438</v>
+      </c>
+      <c r="N545" t="s" s="2">
+        <v>1439</v>
+      </c>
+      <c r="O545" t="s" s="2">
+        <v>1440</v>
+      </c>
+      <c r="P545" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="Q545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R545" s="2"/>
+      <c r="S545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y545" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="Z545" t="s" s="2">
+        <v>1316</v>
+      </c>
+      <c r="AA545" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="AB545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF545" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG545" t="s" s="2">
+        <v>1437</v>
+      </c>
+      <c r="AH545" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI545" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AJ545" t="s" s="2">
+        <v>1318</v>
+      </c>
+      <c r="AK545" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B546" t="s" s="2">
+        <v>1441</v>
+      </c>
+      <c r="C546" t="s" s="2">
+        <v>1441</v>
+      </c>
+      <c r="D546" s="2"/>
+      <c r="E546" t="s" s="2">
+        <v>1320</v>
+      </c>
+      <c r="F546" s="2"/>
+      <c r="G546" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H546" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L546" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M546" t="s" s="2">
+        <v>1442</v>
+      </c>
+      <c r="N546" t="s" s="2">
+        <v>1443</v>
+      </c>
+      <c r="O546" t="s" s="2">
+        <v>1323</v>
+      </c>
+      <c r="P546" t="s" s="2">
+        <v>1324</v>
+      </c>
+      <c r="Q546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R546" s="2"/>
+      <c r="S546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y546" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="Z546" t="s" s="2">
+        <v>1444</v>
+      </c>
+      <c r="AA546" t="s" s="2">
+        <v>1445</v>
+      </c>
+      <c r="AB546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG546" t="s" s="2">
+        <v>1441</v>
+      </c>
+      <c r="AH546" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI546" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ546" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK546" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="B547" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="C547" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="D547" s="2"/>
+      <c r="E547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F547" s="2"/>
+      <c r="G547" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H547" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L547" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="M547" t="s" s="2">
+        <v>1447</v>
+      </c>
+      <c r="N547" t="s" s="2">
+        <v>1448</v>
+      </c>
+      <c r="O547" t="s" s="2">
+        <v>1376</v>
+      </c>
+      <c r="P547" t="s" s="2">
+        <v>1377</v>
+      </c>
+      <c r="Q547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R547" s="2"/>
+      <c r="S547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG547" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="AH547" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI547" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK547" t="s" s="2">
         <v>108</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ci</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:59:07+00:00</t>
+    <t>2026-10-09T10:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:28:47+00:00</t>
+    <t>2026-10-09T10:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:58:12+00:00</t>
+    <t>2026-10-13T12:04:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:04:10+00:00</t>
+    <t>2026-10-13T12:10:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:10:53+00:00</t>
+    <t>2026-10-13T12:17:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:17:17+00:00</t>
+    <t>2026-10-13T12:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:41:55+00:00</t>
+    <t>2026-10-13T13:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
